--- a/ig/mc-add-profiles-dp/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
+++ b/ig/mc-add-profiles-dp/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-16T09:47:39+00:00</t>
+    <t>2023-05-16T10:20:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-add-profiles-dp/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
+++ b/ig/mc-add-profiles-dp/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-16T10:20:11+00:00</t>
+    <t>2023-05-16T15:52:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-add-profiles-dp/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
+++ b/ig/mc-add-profiles-dp/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.3</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-16T15:52:02+00:00</t>
+    <t>2023-05-16T15:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
